--- a/Protocolo.xlsx
+++ b/Protocolo.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maria Juarez\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maria Juarez\Downloads\Claude\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C60CD93-E718-4C39-9045-EAE93840F867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65F5BB4D-F437-4257-93DE-BE3F6F58FC6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Protocolo" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4742" uniqueCount="2158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4751" uniqueCount="2163">
   <si>
     <t>ID</t>
   </si>
@@ -6512,13 +6512,31 @@
   </si>
   <si>
     <t xml:space="preserve"> entrara enterogermina como catalogo aierto (florbasil entrará a protocolo hasta que disminuya el lacteol forte)</t>
+  </si>
+  <si>
+    <t>78099</t>
+  </si>
+  <si>
+    <t>__export__.product_template_78099_39a99780</t>
+  </si>
+  <si>
+    <t>BART H 300MG/12.5MG</t>
+  </si>
+  <si>
+    <t>IRBESARTAN + HIDROCLOROTIAZIDA</t>
+  </si>
+  <si>
+    <t>300MG + 12.5MG</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="44" formatCode="_-&quot;Q&quot;* #,##0.00_-;\-&quot;Q&quot;* #,##0.00_-;_-&quot;Q&quot;* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6534,16 +6552,29 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -6551,18 +6582,60 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="4" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -27605,7 +27678,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9ECB3D7D-793F-434F-AB70-164A6EBB49D9}">
-  <dimension ref="B2:O5"/>
+  <dimension ref="B2:O6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="2:15" x14ac:dyDescent="0.3">
@@ -27699,6 +27772,50 @@
       </c>
       <c r="O5" s="2" t="s">
         <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="B6" s="3" t="s">
+        <v>2158</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>2159</v>
+      </c>
+      <c r="D6" s="5">
+        <v>9303214</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>2160</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>2161</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>2162</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="5">
+        <v>30</v>
+      </c>
+      <c r="J6" s="6">
+        <v>329.3</v>
+      </c>
+      <c r="K6" s="6">
+        <v>235.37</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O6" s="4" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Protocolo.xlsx
+++ b/Protocolo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maria Juarez\Downloads\Claude\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65F5BB4D-F437-4257-93DE-BE3F6F58FC6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DF3F249-652B-4271-BDA5-32B41E78550A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Cambios" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Protocolo!$A$1:$N$467</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Protocolo!$A$1:$N$466</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4751" uniqueCount="2163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4782" uniqueCount="2173">
   <si>
     <t>ID</t>
   </si>
@@ -5548,15 +5548,6 @@
     <t>SINURINSE NINOS KIT (Frasco 120ml y 30 Sobres)</t>
   </si>
   <si>
-    <t>50982</t>
-  </si>
-  <si>
-    <t>__export__.product_template_50982_350c22d5</t>
-  </si>
-  <si>
-    <t>SITAVAN 100MG - CAJA * 30 COMPRIMIDOS</t>
-  </si>
-  <si>
     <t>50689</t>
   </si>
   <si>
@@ -6527,6 +6518,45 @@
   </si>
   <si>
     <t>300MG + 12.5MG</t>
+  </si>
+  <si>
+    <t>79592</t>
+  </si>
+  <si>
+    <t>__export__.product_template_79592_9ae87054</t>
+  </si>
+  <si>
+    <t>SITABET 100MG X 30</t>
+  </si>
+  <si>
+    <t>79602</t>
+  </si>
+  <si>
+    <t>__export__.product_template_79602_34fb312b</t>
+  </si>
+  <si>
+    <t>SITABET M 50/1000MG CAJA * 60 TABLETAS</t>
+  </si>
+  <si>
+    <t>100252</t>
+  </si>
+  <si>
+    <t>__export__.product_template_100252_b47fed1c</t>
+  </si>
+  <si>
+    <t>TENSINOR PLUS 160/12.5/5MG X 30 TABLETAS</t>
+  </si>
+  <si>
+    <t>79981</t>
+  </si>
+  <si>
+    <t>__export__.product_template_79981_b7c71927</t>
+  </si>
+  <si>
+    <t>TENSINOR PLUS 320/25/10 MG X 30 TAB.</t>
+  </si>
+  <si>
+    <t>320MG + 25MG +10MG</t>
   </si>
 </sst>
 </file>
@@ -6560,7 +6590,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6573,8 +6603,14 @@
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor theme="4" tint="0.59999389629810485"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -6610,12 +6646,60 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -6631,6 +6715,24 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7119,7 +7221,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B8C3707-A9DE-471F-806A-6A27068CFE5F}">
-  <dimension ref="A1:N467"/>
+  <dimension ref="A1:N466"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -23765,31 +23867,31 @@
         <v>1838</v>
       </c>
       <c r="D379" s="2" t="s">
-        <v>895</v>
+        <v>1839</v>
       </c>
       <c r="E379" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="F379" s="2" t="s">
-        <v>88</v>
+        <v>479</v>
       </c>
       <c r="G379" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H379" s="2">
-        <v>512.33000000000004</v>
+        <v>279.54000000000002</v>
       </c>
       <c r="I379" s="2">
-        <v>283.13</v>
+        <v>176.05</v>
       </c>
       <c r="J379" s="2" t="s">
         <v>18</v>
       </c>
       <c r="K379" s="2" t="s">
-        <v>39</v>
+        <v>83</v>
       </c>
       <c r="L379" s="2" t="s">
-        <v>39</v>
+        <v>83</v>
       </c>
       <c r="M379" s="2" t="b">
         <v>1</v>
@@ -23800,40 +23902,40 @@
     </row>
     <row r="380" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A380" s="2" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="C380" s="2" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="D380" s="2" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="E380" s="2" t="s">
-        <v>58</v>
+        <v>1121</v>
       </c>
       <c r="F380" s="2" t="s">
-        <v>479</v>
+        <v>106</v>
       </c>
       <c r="G380" s="2">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="H380" s="2">
-        <v>279.54000000000002</v>
+        <v>174.7</v>
       </c>
       <c r="I380" s="2">
-        <v>176.05</v>
+        <v>80.47</v>
       </c>
       <c r="J380" s="2" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="K380" s="2" t="s">
-        <v>83</v>
+        <v>19</v>
       </c>
       <c r="L380" s="2" t="s">
-        <v>83</v>
+        <v>19</v>
       </c>
       <c r="M380" s="2" t="b">
         <v>1</v>
@@ -23844,40 +23946,40 @@
     </row>
     <row r="381" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A381" s="2" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="B381" s="2" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="C381" s="2" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="D381" s="2" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="E381" s="2" t="s">
-        <v>1121</v>
+        <v>1848</v>
       </c>
       <c r="F381" s="2" t="s">
-        <v>106</v>
+        <v>213</v>
       </c>
       <c r="G381" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H381" s="2">
-        <v>174.7</v>
+        <v>200</v>
       </c>
       <c r="I381" s="2">
-        <v>80.47</v>
+        <v>118.99</v>
       </c>
       <c r="J381" s="2" t="s">
-        <v>94</v>
+        <v>138</v>
       </c>
       <c r="K381" s="2" t="s">
-        <v>19</v>
+        <v>108</v>
       </c>
       <c r="L381" s="2" t="s">
-        <v>19</v>
+        <v>108</v>
       </c>
       <c r="M381" s="2" t="b">
         <v>1</v>
@@ -23888,19 +23990,19 @@
     </row>
     <row r="382" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A382" s="2" t="s">
+        <v>1849</v>
+      </c>
+      <c r="B382" s="2" t="s">
+        <v>1850</v>
+      </c>
+      <c r="C382" s="2" t="s">
+        <v>1851</v>
+      </c>
+      <c r="D382" s="2" t="s">
         <v>1847</v>
       </c>
-      <c r="B382" s="2" t="s">
+      <c r="E382" s="2" t="s">
         <v>1848</v>
-      </c>
-      <c r="C382" s="2" t="s">
-        <v>1849</v>
-      </c>
-      <c r="D382" s="2" t="s">
-        <v>1850</v>
-      </c>
-      <c r="E382" s="2" t="s">
-        <v>1851</v>
       </c>
       <c r="F382" s="2" t="s">
         <v>213</v>
@@ -23909,19 +24011,19 @@
         <v>1</v>
       </c>
       <c r="H382" s="2">
-        <v>200</v>
+        <v>241</v>
       </c>
       <c r="I382" s="2">
-        <v>118.99</v>
+        <v>141.15</v>
       </c>
       <c r="J382" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="K382" s="2" t="s">
-        <v>108</v>
+        <v>160</v>
       </c>
       <c r="L382" s="2" t="s">
-        <v>108</v>
+        <v>160</v>
       </c>
       <c r="M382" s="2" t="b">
         <v>1</v>
@@ -23941,10 +24043,10 @@
         <v>1854</v>
       </c>
       <c r="D383" s="2" t="s">
-        <v>1850</v>
+        <v>703</v>
       </c>
       <c r="E383" s="2" t="s">
-        <v>1851</v>
+        <v>708</v>
       </c>
       <c r="F383" s="2" t="s">
         <v>213</v>
@@ -23953,19 +24055,19 @@
         <v>1</v>
       </c>
       <c r="H383" s="2">
-        <v>241</v>
+        <v>162</v>
       </c>
       <c r="I383" s="2">
-        <v>141.15</v>
+        <v>98.55</v>
       </c>
       <c r="J383" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="K383" s="2" t="s">
-        <v>160</v>
+        <v>108</v>
       </c>
       <c r="L383" s="2" t="s">
-        <v>160</v>
+        <v>108</v>
       </c>
       <c r="M383" s="2" t="b">
         <v>1</v>
@@ -23985,40 +24087,40 @@
         <v>1857</v>
       </c>
       <c r="D384" s="2" t="s">
-        <v>703</v>
+        <v>778</v>
       </c>
       <c r="E384" s="2" t="s">
-        <v>708</v>
+        <v>730</v>
       </c>
       <c r="F384" s="2" t="s">
-        <v>213</v>
+        <v>17</v>
       </c>
       <c r="G384" s="2">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="H384" s="2">
-        <v>162</v>
+        <v>198</v>
       </c>
       <c r="I384" s="2">
-        <v>98.55</v>
+        <v>130.43</v>
       </c>
       <c r="J384" s="2" t="s">
-        <v>138</v>
+        <v>18</v>
       </c>
       <c r="K384" s="2" t="s">
-        <v>108</v>
+        <v>39</v>
       </c>
       <c r="L384" s="2" t="s">
-        <v>108</v>
+        <v>39</v>
       </c>
       <c r="M384" s="2" t="b">
         <v>1</v>
       </c>
       <c r="N384" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="385" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="385" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A385" s="2" t="s">
         <v>1858</v>
       </c>
@@ -24029,69 +24131,69 @@
         <v>1860</v>
       </c>
       <c r="D385" s="2" t="s">
-        <v>778</v>
+        <v>1861</v>
       </c>
       <c r="E385" s="2" t="s">
-        <v>730</v>
+        <v>1862</v>
       </c>
       <c r="F385" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="G385" s="2">
+        <v>1</v>
+      </c>
+      <c r="H385" s="2">
+        <v>125</v>
+      </c>
+      <c r="I385" s="2">
+        <v>79.77</v>
+      </c>
+      <c r="J385" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="K385" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="L385" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="M385" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="N385" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="386" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+      <c r="A386" s="2" t="s">
+        <v>1863</v>
+      </c>
+      <c r="B386" s="2" t="s">
+        <v>1864</v>
+      </c>
+      <c r="C386" s="2" t="s">
+        <v>1865</v>
+      </c>
+      <c r="D386" s="2" t="s">
+        <v>1866</v>
+      </c>
+      <c r="E386" s="2" t="s">
+        <v>1031</v>
+      </c>
+      <c r="F386" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G385" s="2">
-        <v>30</v>
-      </c>
-      <c r="H385" s="2">
-        <v>198</v>
-      </c>
-      <c r="I385" s="2">
-        <v>130.43</v>
-      </c>
-      <c r="J385" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K385" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="L385" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="M385" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N385" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="386" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A386" s="2" t="s">
-        <v>1861</v>
-      </c>
-      <c r="B386" s="2" t="s">
-        <v>1862</v>
-      </c>
-      <c r="C386" s="2" t="s">
-        <v>1863</v>
-      </c>
-      <c r="D386" s="2" t="s">
-        <v>1864</v>
-      </c>
-      <c r="E386" s="2" t="s">
-        <v>1865</v>
-      </c>
-      <c r="F386" s="2" t="s">
-        <v>213</v>
-      </c>
       <c r="G386" s="2">
         <v>1</v>
       </c>
       <c r="H386" s="2">
-        <v>125</v>
+        <v>162</v>
       </c>
       <c r="I386" s="2">
-        <v>79.77</v>
+        <v>101.02</v>
       </c>
       <c r="J386" s="2" t="s">
-        <v>138</v>
+        <v>112</v>
       </c>
       <c r="K386" s="2" t="s">
         <v>108</v>
@@ -24108,40 +24210,40 @@
     </row>
     <row r="387" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A387" s="2" t="s">
+        <v>1867</v>
+      </c>
+      <c r="B387" s="2" t="s">
+        <v>1868</v>
+      </c>
+      <c r="C387" s="2" t="s">
+        <v>1869</v>
+      </c>
+      <c r="D387" s="2" t="s">
         <v>1866</v>
       </c>
-      <c r="B387" s="2" t="s">
-        <v>1867</v>
-      </c>
-      <c r="C387" s="2" t="s">
-        <v>1868</v>
-      </c>
-      <c r="D387" s="2" t="s">
-        <v>1869</v>
-      </c>
       <c r="E387" s="2" t="s">
-        <v>1031</v>
+        <v>96</v>
       </c>
       <c r="F387" s="2" t="s">
-        <v>17</v>
+        <v>1870</v>
       </c>
       <c r="G387" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H387" s="2">
-        <v>162</v>
+        <v>64</v>
       </c>
       <c r="I387" s="2">
-        <v>101.02</v>
+        <v>42.29</v>
       </c>
       <c r="J387" s="2" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="K387" s="2" t="s">
-        <v>108</v>
+        <v>350</v>
       </c>
       <c r="L387" s="2" t="s">
-        <v>108</v>
+        <v>60</v>
       </c>
       <c r="M387" s="2" t="b">
         <v>1</v>
@@ -24150,42 +24252,42 @@
         <v>51</v>
       </c>
     </row>
-    <row r="388" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A388" s="2" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="C388" s="2" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="D388" s="2" t="s">
-        <v>1869</v>
+        <v>236</v>
       </c>
       <c r="E388" s="2" t="s">
-        <v>96</v>
+        <v>417</v>
       </c>
       <c r="F388" s="2" t="s">
-        <v>1873</v>
+        <v>166</v>
       </c>
       <c r="G388" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H388" s="2">
-        <v>64</v>
+        <v>255</v>
       </c>
       <c r="I388" s="2">
-        <v>42.29</v>
+        <v>157.16999999999999</v>
       </c>
       <c r="J388" s="2" t="s">
-        <v>37</v>
+        <v>361</v>
       </c>
       <c r="K388" s="2" t="s">
-        <v>350</v>
+        <v>441</v>
       </c>
       <c r="L388" s="2" t="s">
-        <v>60</v>
+        <v>441</v>
       </c>
       <c r="M388" s="2" t="b">
         <v>1</v>
@@ -24194,7 +24296,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="389" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A389" s="2" t="s">
         <v>1874</v>
       </c>
@@ -24205,31 +24307,31 @@
         <v>1876</v>
       </c>
       <c r="D389" s="2" t="s">
-        <v>236</v>
+        <v>423</v>
       </c>
       <c r="E389" s="2" t="s">
-        <v>417</v>
+        <v>284</v>
       </c>
       <c r="F389" s="2" t="s">
-        <v>166</v>
+        <v>514</v>
       </c>
       <c r="G389" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H389" s="2">
-        <v>255</v>
+        <v>66.510000000000005</v>
       </c>
       <c r="I389" s="2">
-        <v>157.16999999999999</v>
+        <v>41.02</v>
       </c>
       <c r="J389" s="2" t="s">
-        <v>361</v>
+        <v>119</v>
       </c>
       <c r="K389" s="2" t="s">
-        <v>441</v>
+        <v>160</v>
       </c>
       <c r="L389" s="2" t="s">
-        <v>441</v>
+        <v>160</v>
       </c>
       <c r="M389" s="2" t="b">
         <v>1</v>
@@ -24249,37 +24351,37 @@
         <v>1879</v>
       </c>
       <c r="D390" s="2" t="s">
-        <v>423</v>
+        <v>492</v>
       </c>
       <c r="E390" s="2" t="s">
-        <v>284</v>
+        <v>493</v>
       </c>
       <c r="F390" s="2" t="s">
-        <v>514</v>
+        <v>17</v>
       </c>
       <c r="G390" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H390" s="2">
-        <v>66.510000000000005</v>
+        <v>304.8</v>
       </c>
       <c r="I390" s="2">
-        <v>41.02</v>
+        <v>191.63</v>
       </c>
       <c r="J390" s="2" t="s">
-        <v>119</v>
+        <v>18</v>
       </c>
       <c r="K390" s="2" t="s">
-        <v>160</v>
+        <v>19</v>
       </c>
       <c r="L390" s="2" t="s">
-        <v>160</v>
+        <v>19</v>
       </c>
       <c r="M390" s="2" t="b">
         <v>1</v>
       </c>
       <c r="N390" s="2" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
     </row>
     <row r="391" spans="1:14" ht="72" x14ac:dyDescent="0.3">
@@ -24293,75 +24395,75 @@
         <v>1882</v>
       </c>
       <c r="D391" s="2" t="s">
-        <v>492</v>
+        <v>1883</v>
       </c>
       <c r="E391" s="2" t="s">
-        <v>493</v>
+        <v>58</v>
       </c>
       <c r="F391" s="2" t="s">
-        <v>17</v>
+        <v>424</v>
       </c>
       <c r="G391" s="2">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H391" s="2">
-        <v>304.8</v>
+        <v>290</v>
       </c>
       <c r="I391" s="2">
-        <v>191.63</v>
+        <v>178.21</v>
       </c>
       <c r="J391" s="2" t="s">
         <v>18</v>
       </c>
       <c r="K391" s="2" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="L391" s="2" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="M391" s="2" t="b">
         <v>1</v>
       </c>
       <c r="N391" s="2" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
     </row>
     <row r="392" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A392" s="2" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="B392" s="2" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
       <c r="C392" s="2" t="s">
-        <v>1885</v>
+        <v>1886</v>
       </c>
       <c r="D392" s="2" t="s">
-        <v>1886</v>
+        <v>964</v>
       </c>
       <c r="E392" s="2" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="F392" s="2" t="s">
-        <v>424</v>
+        <v>28</v>
       </c>
       <c r="G392" s="2">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="H392" s="2">
-        <v>290</v>
+        <v>108</v>
       </c>
       <c r="I392" s="2">
-        <v>178.21</v>
+        <v>77.66</v>
       </c>
       <c r="J392" s="2" t="s">
         <v>18</v>
       </c>
       <c r="K392" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="L392" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="M392" s="2" t="b">
         <v>1</v>
@@ -24381,31 +24483,31 @@
         <v>1889</v>
       </c>
       <c r="D393" s="2" t="s">
-        <v>964</v>
+        <v>507</v>
       </c>
       <c r="E393" s="2" t="s">
-        <v>44</v>
+        <v>199</v>
       </c>
       <c r="F393" s="2" t="s">
-        <v>28</v>
+        <v>106</v>
       </c>
       <c r="G393" s="2">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H393" s="2">
-        <v>108</v>
+        <v>169.78</v>
       </c>
       <c r="I393" s="2">
-        <v>77.66</v>
+        <v>69.69</v>
       </c>
       <c r="J393" s="2" t="s">
         <v>18</v>
       </c>
       <c r="K393" s="2" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="L393" s="2" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="M393" s="2" t="b">
         <v>1</v>
@@ -24428,7 +24530,7 @@
         <v>507</v>
       </c>
       <c r="E394" s="2" t="s">
-        <v>199</v>
+        <v>1030</v>
       </c>
       <c r="F394" s="2" t="s">
         <v>106</v>
@@ -24437,10 +24539,10 @@
         <v>30</v>
       </c>
       <c r="H394" s="2">
-        <v>169.78</v>
+        <v>70</v>
       </c>
       <c r="I394" s="2">
-        <v>69.69</v>
+        <v>27.47</v>
       </c>
       <c r="J394" s="2" t="s">
         <v>18</v>
@@ -24472,7 +24574,7 @@
         <v>507</v>
       </c>
       <c r="E395" s="2" t="s">
-        <v>1030</v>
+        <v>473</v>
       </c>
       <c r="F395" s="2" t="s">
         <v>106</v>
@@ -24481,10 +24583,10 @@
         <v>30</v>
       </c>
       <c r="H395" s="2">
-        <v>70</v>
+        <v>101.43</v>
       </c>
       <c r="I395" s="2">
-        <v>27.47</v>
+        <v>41.8</v>
       </c>
       <c r="J395" s="2" t="s">
         <v>18</v>
@@ -24513,31 +24615,31 @@
         <v>1898</v>
       </c>
       <c r="D396" s="2" t="s">
-        <v>507</v>
+        <v>1519</v>
       </c>
       <c r="E396" s="2" t="s">
-        <v>473</v>
+        <v>1899</v>
       </c>
       <c r="F396" s="2" t="s">
-        <v>106</v>
+        <v>485</v>
       </c>
       <c r="G396" s="2">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="H396" s="2">
-        <v>101.43</v>
+        <v>177</v>
       </c>
       <c r="I396" s="2">
-        <v>41.8</v>
+        <v>119.13</v>
       </c>
       <c r="J396" s="2" t="s">
-        <v>18</v>
+        <v>138</v>
       </c>
       <c r="K396" s="2" t="s">
-        <v>39</v>
+        <v>108</v>
       </c>
       <c r="L396" s="2" t="s">
-        <v>39</v>
+        <v>108</v>
       </c>
       <c r="M396" s="2" t="b">
         <v>1</v>
@@ -24548,34 +24650,34 @@
     </row>
     <row r="397" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A397" s="2" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
       <c r="B397" s="2" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="C397" s="2" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
       <c r="D397" s="2" t="s">
-        <v>1519</v>
+        <v>1903</v>
       </c>
       <c r="E397" s="2" t="s">
-        <v>1902</v>
+        <v>869</v>
       </c>
       <c r="F397" s="2" t="s">
-        <v>485</v>
+        <v>118</v>
       </c>
       <c r="G397" s="2">
         <v>1</v>
       </c>
       <c r="H397" s="2">
-        <v>177</v>
+        <v>371</v>
       </c>
       <c r="I397" s="2">
-        <v>119.13</v>
+        <v>191.17</v>
       </c>
       <c r="J397" s="2" t="s">
-        <v>138</v>
+        <v>112</v>
       </c>
       <c r="K397" s="2" t="s">
         <v>108</v>
@@ -24592,40 +24694,40 @@
     </row>
     <row r="398" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A398" s="2" t="s">
+        <v>1904</v>
+      </c>
+      <c r="B398" s="2" t="s">
+        <v>1905</v>
+      </c>
+      <c r="C398" s="2" t="s">
+        <v>1906</v>
+      </c>
+      <c r="D398" s="2" t="s">
         <v>1903</v>
       </c>
-      <c r="B398" s="2" t="s">
-        <v>1904</v>
-      </c>
-      <c r="C398" s="2" t="s">
-        <v>1905</v>
-      </c>
-      <c r="D398" s="2" t="s">
-        <v>1906</v>
-      </c>
       <c r="E398" s="2" t="s">
-        <v>869</v>
+        <v>62</v>
       </c>
       <c r="F398" s="2" t="s">
         <v>118</v>
       </c>
       <c r="G398" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H398" s="2">
-        <v>371</v>
+        <v>570.57000000000005</v>
       </c>
       <c r="I398" s="2">
-        <v>191.17</v>
+        <v>258.77</v>
       </c>
       <c r="J398" s="2" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="K398" s="2" t="s">
-        <v>108</v>
+        <v>19</v>
       </c>
       <c r="L398" s="2" t="s">
-        <v>108</v>
+        <v>19</v>
       </c>
       <c r="M398" s="2" t="b">
         <v>1</v>
@@ -24645,31 +24747,31 @@
         <v>1909</v>
       </c>
       <c r="D399" s="2" t="s">
-        <v>1906</v>
+        <v>1910</v>
       </c>
       <c r="E399" s="2" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="F399" s="2" t="s">
-        <v>118</v>
+        <v>297</v>
       </c>
       <c r="G399" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H399" s="2">
-        <v>570.57000000000005</v>
+        <v>260</v>
       </c>
       <c r="I399" s="2">
-        <v>258.77</v>
+        <v>175.57</v>
       </c>
       <c r="J399" s="2" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="K399" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="L399" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="M399" s="2" t="b">
         <v>1</v>
@@ -24680,40 +24782,40 @@
     </row>
     <row r="400" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A400" s="2" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="B400" s="2" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="C400" s="2" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
       <c r="D400" s="2" t="s">
-        <v>1913</v>
+        <v>81</v>
       </c>
       <c r="E400" s="2" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="F400" s="2" t="s">
-        <v>297</v>
+        <v>422</v>
       </c>
       <c r="G400" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H400" s="2">
-        <v>260</v>
+        <v>159.4</v>
       </c>
       <c r="I400" s="2">
-        <v>175.57</v>
+        <v>96.84</v>
       </c>
       <c r="J400" s="2" t="s">
         <v>18</v>
       </c>
       <c r="K400" s="2" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="L400" s="2" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M400" s="2" t="b">
         <v>1</v>
@@ -24733,31 +24835,31 @@
         <v>1916</v>
       </c>
       <c r="D401" s="2" t="s">
-        <v>81</v>
+        <v>1917</v>
       </c>
       <c r="E401" s="2" t="s">
-        <v>82</v>
+        <v>32</v>
       </c>
       <c r="F401" s="2" t="s">
-        <v>422</v>
+        <v>55</v>
       </c>
       <c r="G401" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H401" s="2">
-        <v>159.4</v>
+        <v>157</v>
       </c>
       <c r="I401" s="2">
-        <v>96.84</v>
+        <v>93.78</v>
       </c>
       <c r="J401" s="2" t="s">
         <v>18</v>
       </c>
       <c r="K401" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="L401" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="M401" s="2" t="b">
         <v>1</v>
@@ -24766,42 +24868,42 @@
         <v>51</v>
       </c>
     </row>
-    <row r="402" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A402" s="2" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="B402" s="2" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="C402" s="2" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="D402" s="2" t="s">
-        <v>1920</v>
+        <v>1454</v>
       </c>
       <c r="E402" s="2" t="s">
-        <v>32</v>
+        <v>1455</v>
       </c>
       <c r="F402" s="2" t="s">
-        <v>55</v>
+        <v>480</v>
       </c>
       <c r="G402" s="2">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="H402" s="2">
-        <v>157</v>
+        <v>511.65</v>
       </c>
       <c r="I402" s="2">
-        <v>93.78</v>
+        <v>348.1</v>
       </c>
       <c r="J402" s="2" t="s">
         <v>18</v>
       </c>
       <c r="K402" s="2" t="s">
-        <v>25</v>
+        <v>83</v>
       </c>
       <c r="L402" s="2" t="s">
-        <v>25</v>
+        <v>83</v>
       </c>
       <c r="M402" s="2" t="b">
         <v>1</v>
@@ -24810,7 +24912,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="403" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A403" s="2" t="s">
         <v>1921</v>
       </c>
@@ -24821,31 +24923,31 @@
         <v>1923</v>
       </c>
       <c r="D403" s="2" t="s">
-        <v>1454</v>
+        <v>923</v>
       </c>
       <c r="E403" s="2" t="s">
-        <v>1455</v>
+        <v>224</v>
       </c>
       <c r="F403" s="2" t="s">
-        <v>480</v>
+        <v>42</v>
       </c>
       <c r="G403" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H403" s="2">
-        <v>511.65</v>
+        <v>315.82</v>
       </c>
       <c r="I403" s="2">
-        <v>348.1</v>
+        <v>137.86000000000001</v>
       </c>
       <c r="J403" s="2" t="s">
         <v>18</v>
       </c>
       <c r="K403" s="2" t="s">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="L403" s="2" t="s">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="M403" s="2" t="b">
         <v>1</v>
@@ -24865,119 +24967,119 @@
         <v>1926</v>
       </c>
       <c r="D404" s="2" t="s">
-        <v>923</v>
+        <v>1453</v>
       </c>
       <c r="E404" s="2" t="s">
-        <v>224</v>
+        <v>170</v>
       </c>
       <c r="F404" s="2" t="s">
         <v>42</v>
       </c>
       <c r="G404" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H404" s="2">
-        <v>315.82</v>
+        <v>500</v>
       </c>
       <c r="I404" s="2">
-        <v>137.86000000000001</v>
+        <v>190.35</v>
       </c>
       <c r="J404" s="2" t="s">
         <v>18</v>
       </c>
       <c r="K404" s="2" t="s">
-        <v>39</v>
+        <v>83</v>
       </c>
       <c r="L404" s="2" t="s">
-        <v>39</v>
+        <v>83</v>
       </c>
       <c r="M404" s="2" t="b">
         <v>1</v>
       </c>
       <c r="N404" s="2" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
     </row>
     <row r="405" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A405" s="2" t="s">
+        <v>1928</v>
+      </c>
+      <c r="B405" s="2" t="s">
+        <v>1929</v>
+      </c>
+      <c r="C405" s="2" t="s">
+        <v>1930</v>
+      </c>
+      <c r="D405" s="2" t="s">
         <v>1927</v>
       </c>
-      <c r="B405" s="2" t="s">
-        <v>1928</v>
-      </c>
-      <c r="C405" s="2" t="s">
-        <v>1929</v>
-      </c>
-      <c r="D405" s="2" t="s">
-        <v>1453</v>
-      </c>
       <c r="E405" s="2" t="s">
-        <v>170</v>
+        <v>1931</v>
       </c>
       <c r="F405" s="2" t="s">
         <v>42</v>
       </c>
       <c r="G405" s="2">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="H405" s="2">
-        <v>500</v>
+        <v>185.2</v>
       </c>
       <c r="I405" s="2">
-        <v>190.35</v>
+        <v>93.12</v>
       </c>
       <c r="J405" s="2" t="s">
-        <v>18</v>
+        <v>112</v>
       </c>
       <c r="K405" s="2" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="L405" s="2" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="M405" s="2" t="b">
         <v>1</v>
       </c>
       <c r="N405" s="2" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
     </row>
     <row r="406" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A406" s="2" t="s">
+        <v>1932</v>
+      </c>
+      <c r="B406" s="2" t="s">
+        <v>1933</v>
+      </c>
+      <c r="C406" s="2" t="s">
+        <v>1934</v>
+      </c>
+      <c r="D406" s="2" t="s">
+        <v>1927</v>
+      </c>
+      <c r="E406" s="2" t="s">
         <v>1931</v>
-      </c>
-      <c r="B406" s="2" t="s">
-        <v>1932</v>
-      </c>
-      <c r="C406" s="2" t="s">
-        <v>1933</v>
-      </c>
-      <c r="D406" s="2" t="s">
-        <v>1930</v>
-      </c>
-      <c r="E406" s="2" t="s">
-        <v>1934</v>
       </c>
       <c r="F406" s="2" t="s">
         <v>42</v>
       </c>
       <c r="G406" s="2">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="H406" s="2">
-        <v>185.2</v>
+        <v>471.5</v>
       </c>
       <c r="I406" s="2">
-        <v>93.12</v>
+        <v>270.33</v>
       </c>
       <c r="J406" s="2" t="s">
-        <v>112</v>
+        <v>18</v>
       </c>
       <c r="K406" s="2" t="s">
-        <v>108</v>
+        <v>25</v>
       </c>
       <c r="L406" s="2" t="s">
-        <v>108</v>
+        <v>25</v>
       </c>
       <c r="M406" s="2" t="b">
         <v>1</v>
@@ -24997,37 +25099,37 @@
         <v>1937</v>
       </c>
       <c r="D407" s="2" t="s">
-        <v>1930</v>
+        <v>486</v>
       </c>
       <c r="E407" s="2" t="s">
-        <v>1934</v>
+        <v>284</v>
       </c>
       <c r="F407" s="2" t="s">
-        <v>42</v>
+        <v>103</v>
       </c>
       <c r="G407" s="2">
+        <v>1</v>
+      </c>
+      <c r="H407" s="2">
+        <v>90</v>
+      </c>
+      <c r="I407" s="2">
+        <v>32.880000000000003</v>
+      </c>
+      <c r="J407" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="K407" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="L407" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="M407" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="N407" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="H407" s="2">
-        <v>471.5</v>
-      </c>
-      <c r="I407" s="2">
-        <v>270.33</v>
-      </c>
-      <c r="J407" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K407" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L407" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M407" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N407" s="2" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="408" spans="1:14" ht="72" x14ac:dyDescent="0.3">
@@ -25044,28 +25146,28 @@
         <v>486</v>
       </c>
       <c r="E408" s="2" t="s">
-        <v>284</v>
+        <v>75</v>
       </c>
       <c r="F408" s="2" t="s">
         <v>103</v>
       </c>
       <c r="G408" s="2">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="H408" s="2">
-        <v>90</v>
+        <v>738.75</v>
       </c>
       <c r="I408" s="2">
-        <v>32.880000000000003</v>
+        <v>348.16</v>
       </c>
       <c r="J408" s="2" t="s">
-        <v>119</v>
+        <v>18</v>
       </c>
       <c r="K408" s="2" t="s">
-        <v>116</v>
+        <v>39</v>
       </c>
       <c r="L408" s="2" t="s">
-        <v>116</v>
+        <v>39</v>
       </c>
       <c r="M408" s="2" t="b">
         <v>1</v>
@@ -25076,40 +25178,40 @@
     </row>
     <row r="409" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A409" s="2" t="s">
-        <v>1941</v>
+        <v>1943</v>
       </c>
       <c r="B409" s="2" t="s">
-        <v>1942</v>
+        <v>1944</v>
       </c>
       <c r="C409" s="2" t="s">
-        <v>1943</v>
+        <v>1945</v>
       </c>
       <c r="D409" s="2" t="s">
-        <v>486</v>
+        <v>1585</v>
       </c>
       <c r="E409" s="2" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="F409" s="2" t="s">
-        <v>103</v>
+        <v>152</v>
       </c>
       <c r="G409" s="2">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="H409" s="2">
-        <v>738.75</v>
+        <v>20</v>
       </c>
       <c r="I409" s="2">
-        <v>348.16</v>
+        <v>12.87</v>
       </c>
       <c r="J409" s="2" t="s">
         <v>18</v>
       </c>
       <c r="K409" s="2" t="s">
-        <v>39</v>
+        <v>250</v>
       </c>
       <c r="L409" s="2" t="s">
-        <v>39</v>
+        <v>250</v>
       </c>
       <c r="M409" s="2" t="b">
         <v>1</v>
@@ -25129,37 +25231,37 @@
         <v>1948</v>
       </c>
       <c r="D410" s="2" t="s">
-        <v>1585</v>
+        <v>268</v>
       </c>
       <c r="E410" s="2" t="s">
-        <v>96</v>
+        <v>264</v>
       </c>
       <c r="F410" s="2" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="G410" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H410" s="2">
-        <v>20</v>
+        <v>79.599999999999994</v>
       </c>
       <c r="I410" s="2">
-        <v>12.87</v>
+        <v>45.64</v>
       </c>
       <c r="J410" s="2" t="s">
-        <v>18</v>
+        <v>189</v>
       </c>
       <c r="K410" s="2" t="s">
-        <v>250</v>
+        <v>108</v>
       </c>
       <c r="L410" s="2" t="s">
-        <v>250</v>
+        <v>108</v>
       </c>
       <c r="M410" s="2" t="b">
         <v>1</v>
       </c>
       <c r="N410" s="2" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
     </row>
     <row r="411" spans="1:14" ht="72" x14ac:dyDescent="0.3">
@@ -25173,31 +25275,31 @@
         <v>1951</v>
       </c>
       <c r="D411" s="2" t="s">
-        <v>268</v>
+        <v>1952</v>
       </c>
       <c r="E411" s="2" t="s">
-        <v>264</v>
+        <v>1953</v>
       </c>
       <c r="F411" s="2" t="s">
-        <v>165</v>
+        <v>55</v>
       </c>
       <c r="G411" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H411" s="2">
-        <v>79.599999999999994</v>
+        <v>260</v>
       </c>
       <c r="I411" s="2">
-        <v>45.64</v>
+        <v>129.27000000000001</v>
       </c>
       <c r="J411" s="2" t="s">
-        <v>189</v>
+        <v>18</v>
       </c>
       <c r="K411" s="2" t="s">
-        <v>108</v>
+        <v>50</v>
       </c>
       <c r="L411" s="2" t="s">
-        <v>108</v>
+        <v>50</v>
       </c>
       <c r="M411" s="2" t="b">
         <v>1</v>
@@ -25208,40 +25310,40 @@
     </row>
     <row r="412" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A412" s="2" t="s">
-        <v>1952</v>
+        <v>1955</v>
       </c>
       <c r="B412" s="2" t="s">
-        <v>1953</v>
+        <v>1956</v>
       </c>
       <c r="C412" s="2" t="s">
+        <v>1957</v>
+      </c>
+      <c r="D412" s="2" t="s">
         <v>1954</v>
       </c>
-      <c r="D412" s="2" t="s">
-        <v>1955</v>
-      </c>
       <c r="E412" s="2" t="s">
-        <v>1956</v>
+        <v>22</v>
       </c>
       <c r="F412" s="2" t="s">
-        <v>55</v>
+        <v>608</v>
       </c>
       <c r="G412" s="2">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H412" s="2">
-        <v>260</v>
+        <v>145</v>
       </c>
       <c r="I412" s="2">
-        <v>129.27000000000001</v>
+        <v>87</v>
       </c>
       <c r="J412" s="2" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="K412" s="2" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="L412" s="2" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="M412" s="2" t="b">
         <v>1</v>
@@ -25261,31 +25363,31 @@
         <v>1960</v>
       </c>
       <c r="D413" s="2" t="s">
-        <v>1957</v>
+        <v>1954</v>
       </c>
       <c r="E413" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F413" s="2" t="s">
-        <v>608</v>
+        <v>28</v>
       </c>
       <c r="G413" s="2">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H413" s="2">
-        <v>145</v>
+        <v>115</v>
       </c>
       <c r="I413" s="2">
-        <v>87</v>
+        <v>66.17</v>
       </c>
       <c r="J413" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="K413" s="2" t="s">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="L413" s="2" t="s">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="M413" s="2" t="b">
         <v>1</v>
@@ -25305,25 +25407,25 @@
         <v>1963</v>
       </c>
       <c r="D414" s="2" t="s">
-        <v>1957</v>
+        <v>1964</v>
       </c>
       <c r="E414" s="2" t="s">
-        <v>22</v>
+        <v>137</v>
       </c>
       <c r="F414" s="2" t="s">
-        <v>28</v>
+        <v>197</v>
       </c>
       <c r="G414" s="2">
         <v>5</v>
       </c>
       <c r="H414" s="2">
-        <v>115</v>
+        <v>781.2</v>
       </c>
       <c r="I414" s="2">
-        <v>66.17</v>
+        <v>558.04</v>
       </c>
       <c r="J414" s="2" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="K414" s="2" t="s">
         <v>67</v>
@@ -25340,46 +25442,46 @@
     </row>
     <row r="415" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A415" s="2" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="B415" s="2" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="C415" s="2" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="D415" s="2" t="s">
-        <v>1967</v>
+        <v>487</v>
       </c>
       <c r="E415" s="2" t="s">
-        <v>137</v>
+        <v>96</v>
       </c>
       <c r="F415" s="2" t="s">
-        <v>197</v>
+        <v>165</v>
       </c>
       <c r="G415" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H415" s="2">
-        <v>781.2</v>
+        <v>207.45</v>
       </c>
       <c r="I415" s="2">
-        <v>558.04</v>
+        <v>118.4</v>
       </c>
       <c r="J415" s="2" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="K415" s="2" t="s">
-        <v>67</v>
+        <v>235</v>
       </c>
       <c r="L415" s="2" t="s">
-        <v>67</v>
+        <v>235</v>
       </c>
       <c r="M415" s="2" t="b">
         <v>1</v>
       </c>
       <c r="N415" s="2" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
     </row>
     <row r="416" spans="1:14" ht="72" x14ac:dyDescent="0.3">
@@ -25396,72 +25498,72 @@
         <v>487</v>
       </c>
       <c r="E416" s="2" t="s">
-        <v>96</v>
+        <v>1971</v>
       </c>
       <c r="F416" s="2" t="s">
         <v>165</v>
       </c>
       <c r="G416" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H416" s="2">
-        <v>207.45</v>
+        <v>262</v>
       </c>
       <c r="I416" s="2">
-        <v>118.4</v>
+        <v>116.94</v>
       </c>
       <c r="J416" s="2" t="s">
-        <v>18</v>
+        <v>112</v>
       </c>
       <c r="K416" s="2" t="s">
-        <v>235</v>
+        <v>108</v>
       </c>
       <c r="L416" s="2" t="s">
-        <v>235</v>
+        <v>108</v>
       </c>
       <c r="M416" s="2" t="b">
         <v>1</v>
       </c>
       <c r="N416" s="2" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
     </row>
     <row r="417" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A417" s="2" t="s">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="B417" s="2" t="s">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="C417" s="2" t="s">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="D417" s="2" t="s">
-        <v>487</v>
+        <v>1975</v>
       </c>
       <c r="E417" s="2" t="s">
-        <v>1974</v>
+        <v>1976</v>
       </c>
       <c r="F417" s="2" t="s">
-        <v>165</v>
+        <v>878</v>
       </c>
       <c r="G417" s="2">
         <v>1</v>
       </c>
       <c r="H417" s="2">
-        <v>262</v>
+        <v>149</v>
       </c>
       <c r="I417" s="2">
-        <v>116.94</v>
+        <v>91.17</v>
       </c>
       <c r="J417" s="2" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="K417" s="2" t="s">
-        <v>108</v>
+        <v>160</v>
       </c>
       <c r="L417" s="2" t="s">
-        <v>108</v>
+        <v>160</v>
       </c>
       <c r="M417" s="2" t="b">
         <v>1</v>
@@ -25472,40 +25574,40 @@
     </row>
     <row r="418" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A418" s="2" t="s">
-        <v>1975</v>
+        <v>1977</v>
       </c>
       <c r="B418" s="2" t="s">
-        <v>1976</v>
+        <v>1978</v>
       </c>
       <c r="C418" s="2" t="s">
-        <v>1977</v>
+        <v>1979</v>
       </c>
       <c r="D418" s="2" t="s">
-        <v>1978</v>
+        <v>1980</v>
       </c>
       <c r="E418" s="2" t="s">
-        <v>1979</v>
+        <v>1981</v>
       </c>
       <c r="F418" s="2" t="s">
-        <v>878</v>
+        <v>1200</v>
       </c>
       <c r="G418" s="2">
         <v>1</v>
       </c>
       <c r="H418" s="2">
-        <v>149</v>
+        <v>100</v>
       </c>
       <c r="I418" s="2">
-        <v>91.17</v>
+        <v>62.82</v>
       </c>
       <c r="J418" s="2" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="K418" s="2" t="s">
-        <v>160</v>
+        <v>108</v>
       </c>
       <c r="L418" s="2" t="s">
-        <v>160</v>
+        <v>108</v>
       </c>
       <c r="M418" s="2" t="b">
         <v>1</v>
@@ -25514,36 +25616,36 @@
         <v>51</v>
       </c>
     </row>
-    <row r="419" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A419" s="2" t="s">
-        <v>1980</v>
+        <v>1982</v>
       </c>
       <c r="B419" s="2" t="s">
-        <v>1981</v>
+        <v>1983</v>
       </c>
       <c r="C419" s="2" t="s">
-        <v>1982</v>
+        <v>1984</v>
       </c>
       <c r="D419" s="2" t="s">
-        <v>1983</v>
+        <v>1081</v>
       </c>
       <c r="E419" s="2" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="F419" s="2" t="s">
-        <v>1200</v>
+        <v>73</v>
       </c>
       <c r="G419" s="2">
         <v>1</v>
       </c>
       <c r="H419" s="2">
-        <v>100</v>
+        <v>9128.7800000000007</v>
       </c>
       <c r="I419" s="2">
-        <v>62.82</v>
+        <v>0</v>
       </c>
       <c r="J419" s="2" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="K419" s="2" t="s">
         <v>108</v>
@@ -25555,36 +25657,36 @@
         <v>1</v>
       </c>
       <c r="N419" s="2" t="s">
-        <v>51</v>
+        <v>145</v>
       </c>
     </row>
     <row r="420" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A420" s="2" t="s">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="B420" s="2" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="C420" s="2" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="D420" s="2" t="s">
         <v>1081</v>
       </c>
       <c r="E420" s="2" t="s">
-        <v>1988</v>
+        <v>1985</v>
       </c>
       <c r="F420" s="2" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="G420" s="2">
         <v>1</v>
       </c>
       <c r="H420" s="2">
-        <v>9128.7800000000007</v>
+        <v>137</v>
       </c>
       <c r="I420" s="2">
-        <v>0</v>
+        <v>69.570000000000007</v>
       </c>
       <c r="J420" s="2" t="s">
         <v>115</v>
@@ -25599,10 +25701,10 @@
         <v>1</v>
       </c>
       <c r="N420" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="421" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="421" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A421" s="2" t="s">
         <v>1989</v>
       </c>
@@ -25613,25 +25715,25 @@
         <v>1991</v>
       </c>
       <c r="D421" s="2" t="s">
-        <v>1081</v>
+        <v>126</v>
       </c>
       <c r="E421" s="2" t="s">
-        <v>1988</v>
+        <v>1992</v>
       </c>
       <c r="F421" s="2" t="s">
-        <v>55</v>
+        <v>632</v>
       </c>
       <c r="G421" s="2">
         <v>1</v>
       </c>
       <c r="H421" s="2">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="I421" s="2">
-        <v>69.570000000000007</v>
+        <v>84.33</v>
       </c>
       <c r="J421" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K421" s="2" t="s">
         <v>108</v>
@@ -25648,40 +25750,40 @@
     </row>
     <row r="422" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A422" s="2" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="B422" s="2" t="s">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="C422" s="2" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="D422" s="2" t="s">
-        <v>126</v>
+        <v>853</v>
       </c>
       <c r="E422" s="2" t="s">
-        <v>1995</v>
+        <v>913</v>
       </c>
       <c r="F422" s="2" t="s">
-        <v>632</v>
+        <v>661</v>
       </c>
       <c r="G422" s="2">
-        <v>1</v>
+        <v>96</v>
       </c>
       <c r="H422" s="2">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="I422" s="2">
-        <v>84.33</v>
+        <v>109.07</v>
       </c>
       <c r="J422" s="2" t="s">
-        <v>112</v>
+        <v>18</v>
       </c>
       <c r="K422" s="2" t="s">
-        <v>108</v>
+        <v>1648</v>
       </c>
       <c r="L422" s="2" t="s">
-        <v>108</v>
+        <v>1648</v>
       </c>
       <c r="M422" s="2" t="b">
         <v>1</v>
@@ -25690,7 +25792,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="423" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A423" s="2" t="s">
         <v>1996</v>
       </c>
@@ -25701,40 +25803,40 @@
         <v>1998</v>
       </c>
       <c r="D423" s="2" t="s">
-        <v>853</v>
+        <v>805</v>
       </c>
       <c r="E423" s="2" t="s">
-        <v>913</v>
+        <v>395</v>
       </c>
       <c r="F423" s="2" t="s">
         <v>661</v>
       </c>
       <c r="G423" s="2">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="H423" s="2">
-        <v>170</v>
+        <v>176.76</v>
       </c>
       <c r="I423" s="2">
-        <v>109.07</v>
+        <v>131.06</v>
       </c>
       <c r="J423" s="2" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="K423" s="2" t="s">
-        <v>1648</v>
+        <v>87</v>
       </c>
       <c r="L423" s="2" t="s">
-        <v>1648</v>
+        <v>87</v>
       </c>
       <c r="M423" s="2" t="b">
         <v>1</v>
       </c>
       <c r="N423" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="424" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="424" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A424" s="2" t="s">
         <v>1999</v>
       </c>
@@ -25745,51 +25847,51 @@
         <v>2001</v>
       </c>
       <c r="D424" s="2" t="s">
-        <v>805</v>
+        <v>2002</v>
       </c>
       <c r="E424" s="2" t="s">
-        <v>395</v>
+        <v>1665</v>
       </c>
       <c r="F424" s="2" t="s">
-        <v>661</v>
+        <v>103</v>
       </c>
       <c r="G424" s="2">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="H424" s="2">
-        <v>176.76</v>
+        <v>35.549999999999997</v>
       </c>
       <c r="I424" s="2">
-        <v>131.06</v>
+        <v>17.27</v>
       </c>
       <c r="J424" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="K424" s="2" t="s">
-        <v>87</v>
+        <v>302</v>
       </c>
       <c r="L424" s="2" t="s">
-        <v>87</v>
+        <v>302</v>
       </c>
       <c r="M424" s="2" t="b">
         <v>1</v>
       </c>
       <c r="N424" s="2" t="s">
-        <v>145</v>
+        <v>51</v>
       </c>
     </row>
     <row r="425" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A425" s="2" t="s">
+        <v>2003</v>
+      </c>
+      <c r="B425" s="2" t="s">
+        <v>2004</v>
+      </c>
+      <c r="C425" s="2" t="s">
+        <v>2005</v>
+      </c>
+      <c r="D425" s="2" t="s">
         <v>2002</v>
-      </c>
-      <c r="B425" s="2" t="s">
-        <v>2003</v>
-      </c>
-      <c r="C425" s="2" t="s">
-        <v>2004</v>
-      </c>
-      <c r="D425" s="2" t="s">
-        <v>2005</v>
       </c>
       <c r="E425" s="2" t="s">
         <v>1665</v>
@@ -25801,10 +25903,10 @@
         <v>1</v>
       </c>
       <c r="H425" s="2">
-        <v>35.549999999999997</v>
+        <v>26.25</v>
       </c>
       <c r="I425" s="2">
-        <v>17.27</v>
+        <v>12.69</v>
       </c>
       <c r="J425" s="2" t="s">
         <v>49</v>
@@ -25824,46 +25926,46 @@
     </row>
     <row r="426" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A426" s="2" t="s">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="B426" s="2" t="s">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="C426" s="2" t="s">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="D426" s="2" t="s">
-        <v>2005</v>
+        <v>92</v>
       </c>
       <c r="E426" s="2" t="s">
-        <v>1665</v>
+        <v>32</v>
       </c>
       <c r="F426" s="2" t="s">
-        <v>103</v>
+        <v>42</v>
       </c>
       <c r="G426" s="2">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="H426" s="2">
-        <v>26.25</v>
+        <v>289</v>
       </c>
       <c r="I426" s="2">
-        <v>12.69</v>
+        <v>142.84</v>
       </c>
       <c r="J426" s="2" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="K426" s="2" t="s">
-        <v>302</v>
+        <v>63</v>
       </c>
       <c r="L426" s="2" t="s">
-        <v>302</v>
+        <v>63</v>
       </c>
       <c r="M426" s="2" t="b">
         <v>1</v>
       </c>
       <c r="N426" s="2" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
     </row>
     <row r="427" spans="1:14" ht="72" x14ac:dyDescent="0.3">
@@ -25880,72 +25982,72 @@
         <v>92</v>
       </c>
       <c r="E427" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F427" s="2" t="s">
         <v>42</v>
       </c>
       <c r="G427" s="2">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="H427" s="2">
-        <v>289</v>
+        <v>510</v>
       </c>
       <c r="I427" s="2">
-        <v>142.84</v>
+        <v>400.91</v>
       </c>
       <c r="J427" s="2" t="s">
-        <v>37</v>
+        <v>94</v>
       </c>
       <c r="K427" s="2" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="L427" s="2" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="M427" s="2" t="b">
         <v>1</v>
       </c>
       <c r="N427" s="2" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
     </row>
     <row r="428" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A428" s="2" t="s">
+        <v>2015</v>
+      </c>
+      <c r="B428" s="2" t="s">
+        <v>2016</v>
+      </c>
+      <c r="C428" s="2" t="s">
+        <v>2017</v>
+      </c>
+      <c r="D428" s="2" t="s">
         <v>2013</v>
       </c>
-      <c r="B428" s="2" t="s">
+      <c r="E428" s="2" t="s">
         <v>2014</v>
       </c>
-      <c r="C428" s="2" t="s">
-        <v>2015</v>
-      </c>
-      <c r="D428" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E428" s="2" t="s">
-        <v>35</v>
-      </c>
       <c r="F428" s="2" t="s">
-        <v>42</v>
+        <v>139</v>
       </c>
       <c r="G428" s="2">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="H428" s="2">
-        <v>510</v>
+        <v>170</v>
       </c>
       <c r="I428" s="2">
-        <v>400.91</v>
+        <v>116.96</v>
       </c>
       <c r="J428" s="2" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="K428" s="2" t="s">
-        <v>39</v>
+        <v>160</v>
       </c>
       <c r="L428" s="2" t="s">
-        <v>39</v>
+        <v>160</v>
       </c>
       <c r="M428" s="2" t="b">
         <v>1</v>
@@ -25965,31 +26067,31 @@
         <v>2020</v>
       </c>
       <c r="D429" s="2" t="s">
-        <v>2016</v>
+        <v>904</v>
       </c>
       <c r="E429" s="2" t="s">
-        <v>2017</v>
+        <v>75</v>
       </c>
       <c r="F429" s="2" t="s">
-        <v>139</v>
+        <v>88</v>
       </c>
       <c r="G429" s="2">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="H429" s="2">
-        <v>170</v>
+        <v>302.05</v>
       </c>
       <c r="I429" s="2">
-        <v>116.96</v>
+        <v>152.43</v>
       </c>
       <c r="J429" s="2" t="s">
-        <v>119</v>
+        <v>18</v>
       </c>
       <c r="K429" s="2" t="s">
-        <v>160</v>
+        <v>60</v>
       </c>
       <c r="L429" s="2" t="s">
-        <v>160</v>
+        <v>60</v>
       </c>
       <c r="M429" s="2" t="b">
         <v>1</v>
@@ -26000,40 +26102,40 @@
     </row>
     <row r="430" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A430" s="2" t="s">
+        <v>2022</v>
+      </c>
+      <c r="B430" s="2" t="s">
+        <v>2023</v>
+      </c>
+      <c r="C430" s="2" t="s">
+        <v>2024</v>
+      </c>
+      <c r="D430" s="2" t="s">
         <v>2021</v>
       </c>
-      <c r="B430" s="2" t="s">
-        <v>2022</v>
-      </c>
-      <c r="C430" s="2" t="s">
-        <v>2023</v>
-      </c>
-      <c r="D430" s="2" t="s">
-        <v>904</v>
-      </c>
       <c r="E430" s="2" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="F430" s="2" t="s">
-        <v>88</v>
+        <v>55</v>
       </c>
       <c r="G430" s="2">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="H430" s="2">
-        <v>302.05</v>
+        <v>204</v>
       </c>
       <c r="I430" s="2">
-        <v>152.43</v>
+        <v>86.06</v>
       </c>
       <c r="J430" s="2" t="s">
         <v>18</v>
       </c>
       <c r="K430" s="2" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="L430" s="2" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="M430" s="2" t="b">
         <v>1</v>
@@ -26053,31 +26155,31 @@
         <v>2027</v>
       </c>
       <c r="D431" s="2" t="s">
-        <v>2024</v>
+        <v>318</v>
       </c>
       <c r="E431" s="2" t="s">
-        <v>35</v>
+        <v>319</v>
       </c>
       <c r="F431" s="2" t="s">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="G431" s="2">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H431" s="2">
-        <v>204</v>
+        <v>205.15</v>
       </c>
       <c r="I431" s="2">
-        <v>86.06</v>
+        <v>106.2</v>
       </c>
       <c r="J431" s="2" t="s">
         <v>18</v>
       </c>
       <c r="K431" s="2" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="L431" s="2" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="M431" s="2" t="b">
         <v>1</v>
@@ -26097,25 +26199,25 @@
         <v>2030</v>
       </c>
       <c r="D432" s="2" t="s">
-        <v>318</v>
+        <v>594</v>
       </c>
       <c r="E432" s="2" t="s">
-        <v>319</v>
+        <v>869</v>
       </c>
       <c r="F432" s="2" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G432" s="2">
         <v>30</v>
       </c>
       <c r="H432" s="2">
-        <v>205.15</v>
+        <v>465</v>
       </c>
       <c r="I432" s="2">
-        <v>106.2</v>
+        <v>323.33</v>
       </c>
       <c r="J432" s="2" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="K432" s="2" t="s">
         <v>39</v>
@@ -26141,25 +26243,25 @@
         <v>2033</v>
       </c>
       <c r="D433" s="2" t="s">
-        <v>594</v>
+        <v>2034</v>
       </c>
       <c r="E433" s="2" t="s">
-        <v>869</v>
+        <v>2035</v>
       </c>
       <c r="F433" s="2" t="s">
-        <v>76</v>
+        <v>422</v>
       </c>
       <c r="G433" s="2">
         <v>30</v>
       </c>
       <c r="H433" s="2">
-        <v>465</v>
+        <v>294</v>
       </c>
       <c r="I433" s="2">
-        <v>323.33</v>
+        <v>167.4</v>
       </c>
       <c r="J433" s="2" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="K433" s="2" t="s">
         <v>39</v>
@@ -26176,40 +26278,40 @@
     </row>
     <row r="434" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A434" s="2" t="s">
-        <v>2034</v>
+        <v>2036</v>
       </c>
       <c r="B434" s="2" t="s">
-        <v>2035</v>
+        <v>2037</v>
       </c>
       <c r="C434" s="2" t="s">
-        <v>2036</v>
+        <v>2038</v>
       </c>
       <c r="D434" s="2" t="s">
-        <v>2037</v>
+        <v>1120</v>
       </c>
       <c r="E434" s="2" t="s">
-        <v>2038</v>
+        <v>1121</v>
       </c>
       <c r="F434" s="2" t="s">
-        <v>422</v>
+        <v>166</v>
       </c>
       <c r="G434" s="2">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="H434" s="2">
-        <v>294</v>
+        <v>158</v>
       </c>
       <c r="I434" s="2">
-        <v>167.4</v>
+        <v>83.17</v>
       </c>
       <c r="J434" s="2" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="K434" s="2" t="s">
-        <v>39</v>
+        <v>302</v>
       </c>
       <c r="L434" s="2" t="s">
-        <v>39</v>
+        <v>302</v>
       </c>
       <c r="M434" s="2" t="b">
         <v>1</v>
@@ -26229,31 +26331,31 @@
         <v>2041</v>
       </c>
       <c r="D435" s="2" t="s">
-        <v>1120</v>
+        <v>1187</v>
       </c>
       <c r="E435" s="2" t="s">
-        <v>1121</v>
+        <v>2042</v>
       </c>
       <c r="F435" s="2" t="s">
-        <v>166</v>
+        <v>55</v>
       </c>
       <c r="G435" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H435" s="2">
-        <v>158</v>
+        <v>326</v>
       </c>
       <c r="I435" s="2">
-        <v>83.17</v>
+        <v>160.83000000000001</v>
       </c>
       <c r="J435" s="2" t="s">
-        <v>94</v>
+        <v>361</v>
       </c>
       <c r="K435" s="2" t="s">
-        <v>302</v>
+        <v>235</v>
       </c>
       <c r="L435" s="2" t="s">
-        <v>302</v>
+        <v>235</v>
       </c>
       <c r="M435" s="2" t="b">
         <v>1</v>
@@ -26264,40 +26366,40 @@
     </row>
     <row r="436" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A436" s="2" t="s">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="B436" s="2" t="s">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="C436" s="2" t="s">
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="D436" s="2" t="s">
         <v>1187</v>
       </c>
       <c r="E436" s="2" t="s">
-        <v>2045</v>
+        <v>2046</v>
       </c>
       <c r="F436" s="2" t="s">
         <v>55</v>
       </c>
       <c r="G436" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H436" s="2">
-        <v>326</v>
+        <v>311</v>
       </c>
       <c r="I436" s="2">
-        <v>160.83000000000001</v>
+        <v>138.83000000000001</v>
       </c>
       <c r="J436" s="2" t="s">
-        <v>361</v>
+        <v>119</v>
       </c>
       <c r="K436" s="2" t="s">
-        <v>235</v>
+        <v>160</v>
       </c>
       <c r="L436" s="2" t="s">
-        <v>235</v>
+        <v>160</v>
       </c>
       <c r="M436" s="2" t="b">
         <v>1</v>
@@ -26306,21 +26408,21 @@
         <v>51</v>
       </c>
     </row>
-    <row r="437" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A437" s="2" t="s">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="B437" s="2" t="s">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="C437" s="2" t="s">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="D437" s="2" t="s">
-        <v>1187</v>
+        <v>2050</v>
       </c>
       <c r="E437" s="2" t="s">
-        <v>2049</v>
+        <v>110</v>
       </c>
       <c r="F437" s="2" t="s">
         <v>55</v>
@@ -26332,7 +26434,7 @@
         <v>311</v>
       </c>
       <c r="I437" s="2">
-        <v>138.83000000000001</v>
+        <v>166.16</v>
       </c>
       <c r="J437" s="2" t="s">
         <v>119</v>
@@ -26350,42 +26452,42 @@
         <v>51</v>
       </c>
     </row>
-    <row r="438" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A438" s="2" t="s">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="B438" s="2" t="s">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="C438" s="2" t="s">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="D438" s="2" t="s">
-        <v>2053</v>
+        <v>351</v>
       </c>
       <c r="E438" s="2" t="s">
-        <v>110</v>
+        <v>1032</v>
       </c>
       <c r="F438" s="2" t="s">
-        <v>55</v>
+        <v>165</v>
       </c>
       <c r="G438" s="2">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="H438" s="2">
-        <v>311</v>
+        <v>518</v>
       </c>
       <c r="I438" s="2">
-        <v>166.16</v>
+        <v>232.76</v>
       </c>
       <c r="J438" s="2" t="s">
-        <v>119</v>
+        <v>18</v>
       </c>
       <c r="K438" s="2" t="s">
-        <v>160</v>
+        <v>39</v>
       </c>
       <c r="L438" s="2" t="s">
-        <v>160</v>
+        <v>39</v>
       </c>
       <c r="M438" s="2" t="b">
         <v>1</v>
@@ -26394,7 +26496,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="439" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A439" s="2" t="s">
         <v>2054</v>
       </c>
@@ -26405,10 +26507,10 @@
         <v>2056</v>
       </c>
       <c r="D439" s="2" t="s">
-        <v>351</v>
+        <v>1033</v>
       </c>
       <c r="E439" s="2" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="F439" s="2" t="s">
         <v>165</v>
@@ -26417,10 +26519,10 @@
         <v>30</v>
       </c>
       <c r="H439" s="2">
-        <v>518</v>
+        <v>548</v>
       </c>
       <c r="I439" s="2">
-        <v>232.76</v>
+        <v>256.35000000000002</v>
       </c>
       <c r="J439" s="2" t="s">
         <v>18</v>
@@ -26461,10 +26563,10 @@
         <v>30</v>
       </c>
       <c r="H440" s="2">
-        <v>548</v>
+        <v>526.92999999999995</v>
       </c>
       <c r="I440" s="2">
-        <v>256.35000000000002</v>
+        <v>239.1</v>
       </c>
       <c r="J440" s="2" t="s">
         <v>18</v>
@@ -26482,42 +26584,42 @@
         <v>51</v>
       </c>
     </row>
-    <row r="441" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A441" s="2" t="s">
+        <v>2062</v>
+      </c>
+      <c r="B441" s="2" t="s">
+        <v>2063</v>
+      </c>
+      <c r="C441" s="2" t="s">
+        <v>2064</v>
+      </c>
+      <c r="D441" s="2" t="s">
         <v>2060</v>
       </c>
-      <c r="B441" s="2" t="s">
+      <c r="E441" s="2" t="s">
         <v>2061</v>
       </c>
-      <c r="C441" s="2" t="s">
-        <v>2062</v>
-      </c>
-      <c r="D441" s="2" t="s">
-        <v>1033</v>
-      </c>
-      <c r="E441" s="2" t="s">
-        <v>1034</v>
-      </c>
       <c r="F441" s="2" t="s">
-        <v>165</v>
+        <v>2006</v>
       </c>
       <c r="G441" s="2">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="H441" s="2">
-        <v>526.92999999999995</v>
+        <v>133</v>
       </c>
       <c r="I441" s="2">
-        <v>239.1</v>
+        <v>74.960000000000008</v>
       </c>
       <c r="J441" s="2" t="s">
-        <v>18</v>
+        <v>465</v>
       </c>
       <c r="K441" s="2" t="s">
-        <v>39</v>
+        <v>108</v>
       </c>
       <c r="L441" s="2" t="s">
-        <v>39</v>
+        <v>108</v>
       </c>
       <c r="M441" s="2" t="b">
         <v>1</v>
@@ -26528,40 +26630,40 @@
     </row>
     <row r="442" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A442" s="2" t="s">
+        <v>2067</v>
+      </c>
+      <c r="B442" s="2" t="s">
+        <v>2068</v>
+      </c>
+      <c r="C442" s="2" t="s">
+        <v>2069</v>
+      </c>
+      <c r="D442" s="2" t="s">
         <v>2065</v>
       </c>
-      <c r="B442" s="2" t="s">
+      <c r="E442" s="2" t="s">
         <v>2066</v>
       </c>
-      <c r="C442" s="2" t="s">
-        <v>2067</v>
-      </c>
-      <c r="D442" s="2" t="s">
-        <v>2063</v>
-      </c>
-      <c r="E442" s="2" t="s">
-        <v>2064</v>
-      </c>
       <c r="F442" s="2" t="s">
-        <v>2009</v>
+        <v>409</v>
       </c>
       <c r="G442" s="2">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="H442" s="2">
-        <v>133</v>
+        <v>218.9</v>
       </c>
       <c r="I442" s="2">
-        <v>74.960000000000008</v>
+        <v>137.58000000000001</v>
       </c>
       <c r="J442" s="2" t="s">
-        <v>465</v>
+        <v>18</v>
       </c>
       <c r="K442" s="2" t="s">
-        <v>108</v>
+        <v>39</v>
       </c>
       <c r="L442" s="2" t="s">
-        <v>108</v>
+        <v>39</v>
       </c>
       <c r="M442" s="2" t="b">
         <v>1</v>
@@ -26581,22 +26683,22 @@
         <v>2072</v>
       </c>
       <c r="D443" s="2" t="s">
-        <v>2068</v>
+        <v>820</v>
       </c>
       <c r="E443" s="2" t="s">
-        <v>2069</v>
+        <v>47</v>
       </c>
       <c r="F443" s="2" t="s">
-        <v>409</v>
+        <v>42</v>
       </c>
       <c r="G443" s="2">
         <v>30</v>
       </c>
       <c r="H443" s="2">
-        <v>218.9</v>
+        <v>472.29</v>
       </c>
       <c r="I443" s="2">
-        <v>137.58000000000001</v>
+        <v>182.13</v>
       </c>
       <c r="J443" s="2" t="s">
         <v>18</v>
@@ -26611,7 +26713,7 @@
         <v>1</v>
       </c>
       <c r="N443" s="2" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
     </row>
     <row r="444" spans="1:14" ht="72" x14ac:dyDescent="0.3">
@@ -26625,10 +26727,10 @@
         <v>2075</v>
       </c>
       <c r="D444" s="2" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="E444" s="2" t="s">
-        <v>47</v>
+        <v>462</v>
       </c>
       <c r="F444" s="2" t="s">
         <v>42</v>
@@ -26637,10 +26739,10 @@
         <v>30</v>
       </c>
       <c r="H444" s="2">
-        <v>472.29</v>
+        <v>600</v>
       </c>
       <c r="I444" s="2">
-        <v>182.13</v>
+        <v>266.13</v>
       </c>
       <c r="J444" s="2" t="s">
         <v>18</v>
@@ -26660,84 +26762,84 @@
     </row>
     <row r="445" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A445" s="2" t="s">
+        <v>2077</v>
+      </c>
+      <c r="B445" s="2" t="s">
+        <v>2078</v>
+      </c>
+      <c r="C445" s="2" t="s">
+        <v>2079</v>
+      </c>
+      <c r="D445" s="2" t="s">
         <v>2076</v>
       </c>
-      <c r="B445" s="2" t="s">
-        <v>2077</v>
-      </c>
-      <c r="C445" s="2" t="s">
-        <v>2078</v>
-      </c>
-      <c r="D445" s="2" t="s">
-        <v>821</v>
-      </c>
       <c r="E445" s="2" t="s">
-        <v>462</v>
+        <v>2080</v>
       </c>
       <c r="F445" s="2" t="s">
-        <v>42</v>
+        <v>922</v>
       </c>
       <c r="G445" s="2">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="H445" s="2">
-        <v>600</v>
+        <v>260</v>
       </c>
       <c r="I445" s="2">
-        <v>266.13</v>
+        <v>165.46</v>
       </c>
       <c r="J445" s="2" t="s">
-        <v>18</v>
+        <v>144</v>
       </c>
       <c r="K445" s="2" t="s">
-        <v>39</v>
+        <v>160</v>
       </c>
       <c r="L445" s="2" t="s">
-        <v>39</v>
+        <v>160</v>
       </c>
       <c r="M445" s="2" t="b">
         <v>1</v>
       </c>
       <c r="N445" s="2" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
     </row>
     <row r="446" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A446" s="2" t="s">
-        <v>2080</v>
+        <v>2081</v>
       </c>
       <c r="B446" s="2" t="s">
-        <v>2081</v>
+        <v>2082</v>
       </c>
       <c r="C446" s="2" t="s">
-        <v>2082</v>
+        <v>2083</v>
       </c>
       <c r="D446" s="2" t="s">
-        <v>2079</v>
+        <v>198</v>
       </c>
       <c r="E446" s="2" t="s">
-        <v>2083</v>
+        <v>199</v>
       </c>
       <c r="F446" s="2" t="s">
-        <v>922</v>
+        <v>192</v>
       </c>
       <c r="G446" s="2">
         <v>1</v>
       </c>
       <c r="H446" s="2">
-        <v>260</v>
+        <v>135.37</v>
       </c>
       <c r="I446" s="2">
-        <v>165.46</v>
+        <v>76.64</v>
       </c>
       <c r="J446" s="2" t="s">
-        <v>144</v>
+        <v>200</v>
       </c>
       <c r="K446" s="2" t="s">
-        <v>160</v>
+        <v>116</v>
       </c>
       <c r="L446" s="2" t="s">
-        <v>160</v>
+        <v>116</v>
       </c>
       <c r="M446" s="2" t="b">
         <v>1</v>
@@ -26757,31 +26859,31 @@
         <v>2086</v>
       </c>
       <c r="D447" s="2" t="s">
-        <v>198</v>
+        <v>367</v>
       </c>
       <c r="E447" s="2" t="s">
-        <v>199</v>
+        <v>400</v>
       </c>
       <c r="F447" s="2" t="s">
-        <v>192</v>
+        <v>28</v>
       </c>
       <c r="G447" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H447" s="2">
-        <v>135.37</v>
+        <v>370</v>
       </c>
       <c r="I447" s="2">
-        <v>76.64</v>
+        <v>261.41000000000003</v>
       </c>
       <c r="J447" s="2" t="s">
-        <v>200</v>
+        <v>429</v>
       </c>
       <c r="K447" s="2" t="s">
-        <v>116</v>
+        <v>67</v>
       </c>
       <c r="L447" s="2" t="s">
-        <v>116</v>
+        <v>67</v>
       </c>
       <c r="M447" s="2" t="b">
         <v>1</v>
@@ -26801,31 +26903,31 @@
         <v>2089</v>
       </c>
       <c r="D448" s="2" t="s">
-        <v>367</v>
+        <v>2090</v>
       </c>
       <c r="E448" s="2" t="s">
-        <v>400</v>
+        <v>56</v>
       </c>
       <c r="F448" s="2" t="s">
-        <v>28</v>
+        <v>1082</v>
       </c>
       <c r="G448" s="2">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="H448" s="2">
-        <v>370</v>
+        <v>135</v>
       </c>
       <c r="I448" s="2">
-        <v>261.41000000000003</v>
+        <v>88.68</v>
       </c>
       <c r="J448" s="2" t="s">
-        <v>429</v>
+        <v>18</v>
       </c>
       <c r="K448" s="2" t="s">
-        <v>67</v>
+        <v>435</v>
       </c>
       <c r="L448" s="2" t="s">
-        <v>67</v>
+        <v>435</v>
       </c>
       <c r="M448" s="2" t="b">
         <v>1</v>
@@ -26836,46 +26938,46 @@
     </row>
     <row r="449" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A449" s="2" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="B449" s="2" t="s">
-        <v>2091</v>
+        <v>2092</v>
       </c>
       <c r="C449" s="2" t="s">
-        <v>2092</v>
+        <v>2093</v>
       </c>
       <c r="D449" s="2" t="s">
-        <v>2093</v>
+        <v>71</v>
       </c>
       <c r="E449" s="2" t="s">
-        <v>56</v>
+        <v>877</v>
       </c>
       <c r="F449" s="2" t="s">
-        <v>1082</v>
+        <v>42</v>
       </c>
       <c r="G449" s="2">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="H449" s="2">
-        <v>135</v>
+        <v>95</v>
       </c>
       <c r="I449" s="2">
-        <v>88.68</v>
+        <v>49.11</v>
       </c>
       <c r="J449" s="2" t="s">
-        <v>18</v>
+        <v>108</v>
       </c>
       <c r="K449" s="2" t="s">
-        <v>435</v>
+        <v>116</v>
       </c>
       <c r="L449" s="2" t="s">
-        <v>435</v>
+        <v>116</v>
       </c>
       <c r="M449" s="2" t="b">
         <v>1</v>
       </c>
       <c r="N449" s="2" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
     </row>
     <row r="450" spans="1:14" ht="72" x14ac:dyDescent="0.3">
@@ -26892,37 +26994,37 @@
         <v>71</v>
       </c>
       <c r="E450" s="2" t="s">
-        <v>877</v>
+        <v>41</v>
       </c>
       <c r="F450" s="2" t="s">
         <v>42</v>
       </c>
       <c r="G450" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H450" s="2">
-        <v>95</v>
+        <v>137</v>
       </c>
       <c r="I450" s="2">
-        <v>49.11</v>
+        <v>88.39</v>
       </c>
       <c r="J450" s="2" t="s">
-        <v>108</v>
+        <v>18</v>
       </c>
       <c r="K450" s="2" t="s">
-        <v>116</v>
+        <v>19</v>
       </c>
       <c r="L450" s="2" t="s">
-        <v>116</v>
+        <v>19</v>
       </c>
       <c r="M450" s="2" t="b">
         <v>1</v>
       </c>
       <c r="N450" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="451" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="451" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A451" s="2" t="s">
         <v>2097</v>
       </c>
@@ -26933,31 +27035,31 @@
         <v>2099</v>
       </c>
       <c r="D451" s="2" t="s">
-        <v>71</v>
+        <v>762</v>
       </c>
       <c r="E451" s="2" t="s">
-        <v>41</v>
+        <v>840</v>
       </c>
       <c r="F451" s="2" t="s">
         <v>42</v>
       </c>
       <c r="G451" s="2">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H451" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I451" s="2">
-        <v>88.39</v>
+        <v>96.070000000000007</v>
       </c>
       <c r="J451" s="2" t="s">
-        <v>18</v>
+        <v>211</v>
       </c>
       <c r="K451" s="2" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="L451" s="2" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="M451" s="2" t="b">
         <v>1</v>
@@ -26966,42 +27068,42 @@
         <v>51</v>
       </c>
     </row>
-    <row r="452" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A452" s="2" t="s">
+        <v>2101</v>
+      </c>
+      <c r="B452" s="2" t="s">
+        <v>2102</v>
+      </c>
+      <c r="C452" s="2" t="s">
+        <v>2103</v>
+      </c>
+      <c r="D452" s="2" t="s">
         <v>2100</v>
       </c>
-      <c r="B452" s="2" t="s">
-        <v>2101</v>
-      </c>
-      <c r="C452" s="2" t="s">
-        <v>2102</v>
-      </c>
-      <c r="D452" s="2" t="s">
-        <v>762</v>
-      </c>
       <c r="E452" s="2" t="s">
-        <v>840</v>
+        <v>754</v>
       </c>
       <c r="F452" s="2" t="s">
-        <v>42</v>
+        <v>485</v>
       </c>
       <c r="G452" s="2">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="H452" s="2">
-        <v>139</v>
+        <v>250</v>
       </c>
       <c r="I452" s="2">
-        <v>96.070000000000007</v>
+        <v>157.94999999999999</v>
       </c>
       <c r="J452" s="2" t="s">
-        <v>211</v>
+        <v>138</v>
       </c>
       <c r="K452" s="2" t="s">
-        <v>39</v>
+        <v>108</v>
       </c>
       <c r="L452" s="2" t="s">
-        <v>39</v>
+        <v>108</v>
       </c>
       <c r="M452" s="2" t="b">
         <v>1</v>
@@ -27021,31 +27123,31 @@
         <v>2106</v>
       </c>
       <c r="D453" s="2" t="s">
-        <v>2103</v>
+        <v>1941</v>
       </c>
       <c r="E453" s="2" t="s">
-        <v>754</v>
+        <v>1942</v>
       </c>
       <c r="F453" s="2" t="s">
-        <v>485</v>
+        <v>57</v>
       </c>
       <c r="G453" s="2">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="H453" s="2">
-        <v>250</v>
+        <v>454.48</v>
       </c>
       <c r="I453" s="2">
-        <v>157.94999999999999</v>
+        <v>295.05</v>
       </c>
       <c r="J453" s="2" t="s">
-        <v>138</v>
+        <v>18</v>
       </c>
       <c r="K453" s="2" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="L453" s="2" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="M453" s="2" t="b">
         <v>1</v>
@@ -27065,31 +27167,31 @@
         <v>2109</v>
       </c>
       <c r="D454" s="2" t="s">
-        <v>1944</v>
+        <v>444</v>
       </c>
       <c r="E454" s="2" t="s">
-        <v>1945</v>
+        <v>35</v>
       </c>
       <c r="F454" s="2" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="G454" s="2">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="H454" s="2">
-        <v>454.48</v>
+        <v>195</v>
       </c>
       <c r="I454" s="2">
-        <v>295.05</v>
+        <v>110.08</v>
       </c>
       <c r="J454" s="2" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="K454" s="2" t="s">
-        <v>83</v>
+        <v>33</v>
       </c>
       <c r="L454" s="2" t="s">
-        <v>83</v>
+        <v>508</v>
       </c>
       <c r="M454" s="2" t="b">
         <v>1</v>
@@ -27118,22 +27220,22 @@
         <v>36</v>
       </c>
       <c r="G455" s="2">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H455" s="2">
-        <v>195</v>
+        <v>591.79999999999995</v>
       </c>
       <c r="I455" s="2">
-        <v>110.08</v>
+        <v>331.41</v>
       </c>
       <c r="J455" s="2" t="s">
         <v>37</v>
       </c>
       <c r="K455" s="2" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="L455" s="2" t="s">
-        <v>508</v>
+        <v>39</v>
       </c>
       <c r="M455" s="2" t="b">
         <v>1</v>
@@ -27156,7 +27258,7 @@
         <v>444</v>
       </c>
       <c r="E456" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F456" s="2" t="s">
         <v>36</v>
@@ -27165,13 +27267,13 @@
         <v>30</v>
       </c>
       <c r="H456" s="2">
-        <v>591.79999999999995</v>
+        <v>563.29999999999995</v>
       </c>
       <c r="I456" s="2">
-        <v>331.41</v>
+        <v>377.06</v>
       </c>
       <c r="J456" s="2" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="K456" s="2" t="s">
         <v>39</v>
@@ -27197,31 +27299,31 @@
         <v>2118</v>
       </c>
       <c r="D457" s="2" t="s">
-        <v>444</v>
+        <v>2119</v>
       </c>
       <c r="E457" s="2" t="s">
-        <v>41</v>
+        <v>707</v>
       </c>
       <c r="F457" s="2" t="s">
-        <v>36</v>
+        <v>165</v>
       </c>
       <c r="G457" s="2">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="H457" s="2">
-        <v>563.29999999999995</v>
+        <v>102.65</v>
       </c>
       <c r="I457" s="2">
-        <v>377.06</v>
+        <v>57.84</v>
       </c>
       <c r="J457" s="2" t="s">
-        <v>18</v>
+        <v>138</v>
       </c>
       <c r="K457" s="2" t="s">
-        <v>39</v>
+        <v>108</v>
       </c>
       <c r="L457" s="2" t="s">
-        <v>39</v>
+        <v>108</v>
       </c>
       <c r="M457" s="2" t="b">
         <v>1</v>
@@ -27232,19 +27334,19 @@
     </row>
     <row r="458" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A458" s="2" t="s">
-        <v>2119</v>
+        <v>2120</v>
       </c>
       <c r="B458" s="2" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
       <c r="C458" s="2" t="s">
-        <v>2121</v>
+        <v>2122</v>
       </c>
       <c r="D458" s="2" t="s">
-        <v>2122</v>
+        <v>278</v>
       </c>
       <c r="E458" s="2" t="s">
-        <v>707</v>
+        <v>1174</v>
       </c>
       <c r="F458" s="2" t="s">
         <v>165</v>
@@ -27253,13 +27355,13 @@
         <v>1</v>
       </c>
       <c r="H458" s="2">
-        <v>102.65</v>
+        <v>130</v>
       </c>
       <c r="I458" s="2">
-        <v>57.84</v>
+        <v>69.100000000000009</v>
       </c>
       <c r="J458" s="2" t="s">
-        <v>138</v>
+        <v>189</v>
       </c>
       <c r="K458" s="2" t="s">
         <v>108</v>
@@ -27285,10 +27387,10 @@
         <v>2125</v>
       </c>
       <c r="D459" s="2" t="s">
-        <v>278</v>
+        <v>2126</v>
       </c>
       <c r="E459" s="2" t="s">
-        <v>1174</v>
+        <v>1628</v>
       </c>
       <c r="F459" s="2" t="s">
         <v>165</v>
@@ -27297,19 +27399,19 @@
         <v>1</v>
       </c>
       <c r="H459" s="2">
-        <v>130</v>
+        <v>168</v>
       </c>
       <c r="I459" s="2">
-        <v>69.100000000000009</v>
+        <v>90.64</v>
       </c>
       <c r="J459" s="2" t="s">
-        <v>189</v>
+        <v>140</v>
       </c>
       <c r="K459" s="2" t="s">
-        <v>108</v>
+        <v>160</v>
       </c>
       <c r="L459" s="2" t="s">
-        <v>108</v>
+        <v>160</v>
       </c>
       <c r="M459" s="2" t="b">
         <v>1</v>
@@ -27320,40 +27422,40 @@
     </row>
     <row r="460" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A460" s="2" t="s">
-        <v>2126</v>
+        <v>2127</v>
       </c>
       <c r="B460" s="2" t="s">
-        <v>2127</v>
+        <v>2128</v>
       </c>
       <c r="C460" s="2" t="s">
-        <v>2128</v>
+        <v>2129</v>
       </c>
       <c r="D460" s="2" t="s">
-        <v>2129</v>
+        <v>868</v>
       </c>
       <c r="E460" s="2" t="s">
-        <v>1628</v>
+        <v>226</v>
       </c>
       <c r="F460" s="2" t="s">
-        <v>165</v>
+        <v>48</v>
       </c>
       <c r="G460" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H460" s="2">
-        <v>168</v>
+        <v>341.64</v>
       </c>
       <c r="I460" s="2">
-        <v>90.64</v>
+        <v>228.8</v>
       </c>
       <c r="J460" s="2" t="s">
-        <v>140</v>
+        <v>18</v>
       </c>
       <c r="K460" s="2" t="s">
-        <v>160</v>
+        <v>19</v>
       </c>
       <c r="L460" s="2" t="s">
-        <v>160</v>
+        <v>19</v>
       </c>
       <c r="M460" s="2" t="b">
         <v>1</v>
@@ -27376,7 +27478,7 @@
         <v>868</v>
       </c>
       <c r="E461" s="2" t="s">
-        <v>226</v>
+        <v>869</v>
       </c>
       <c r="F461" s="2" t="s">
         <v>48</v>
@@ -27385,10 +27487,10 @@
         <v>10</v>
       </c>
       <c r="H461" s="2">
-        <v>341.64</v>
+        <v>135</v>
       </c>
       <c r="I461" s="2">
-        <v>228.8</v>
+        <v>76.510000000000005</v>
       </c>
       <c r="J461" s="2" t="s">
         <v>18</v>
@@ -27417,37 +27519,37 @@
         <v>2135</v>
       </c>
       <c r="D462" s="2" t="s">
-        <v>868</v>
+        <v>587</v>
       </c>
       <c r="E462" s="2" t="s">
-        <v>869</v>
+        <v>588</v>
       </c>
       <c r="F462" s="2" t="s">
-        <v>48</v>
+        <v>213</v>
       </c>
       <c r="G462" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H462" s="2">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="I462" s="2">
-        <v>76.510000000000005</v>
+        <v>96.240000000000009</v>
       </c>
       <c r="J462" s="2" t="s">
-        <v>18</v>
+        <v>138</v>
       </c>
       <c r="K462" s="2" t="s">
-        <v>19</v>
+        <v>108</v>
       </c>
       <c r="L462" s="2" t="s">
-        <v>19</v>
+        <v>108</v>
       </c>
       <c r="M462" s="2" t="b">
         <v>1</v>
       </c>
       <c r="N462" s="2" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
     </row>
     <row r="463" spans="1:14" ht="72" x14ac:dyDescent="0.3">
@@ -27461,31 +27563,31 @@
         <v>2138</v>
       </c>
       <c r="D463" s="2" t="s">
-        <v>587</v>
+        <v>126</v>
       </c>
       <c r="E463" s="2" t="s">
-        <v>588</v>
+        <v>177</v>
       </c>
       <c r="F463" s="2" t="s">
-        <v>213</v>
+        <v>509</v>
       </c>
       <c r="G463" s="2">
         <v>1</v>
       </c>
       <c r="H463" s="2">
-        <v>157</v>
+        <v>5</v>
       </c>
       <c r="I463" s="2">
-        <v>96.240000000000009</v>
+        <v>2.7</v>
       </c>
       <c r="J463" s="2" t="s">
-        <v>138</v>
+        <v>18</v>
       </c>
       <c r="K463" s="2" t="s">
-        <v>108</v>
+        <v>14</v>
       </c>
       <c r="L463" s="2" t="s">
-        <v>108</v>
+        <v>25</v>
       </c>
       <c r="M463" s="2" t="b">
         <v>1</v>
@@ -27514,19 +27616,19 @@
         <v>509</v>
       </c>
       <c r="G464" s="2">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="H464" s="2">
-        <v>5</v>
+        <v>95</v>
       </c>
       <c r="I464" s="2">
-        <v>2.7</v>
+        <v>49.99</v>
       </c>
       <c r="J464" s="2" t="s">
         <v>18</v>
       </c>
       <c r="K464" s="2" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="L464" s="2" t="s">
         <v>25</v>
@@ -27535,7 +27637,7 @@
         <v>1</v>
       </c>
       <c r="N464" s="2" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
     </row>
     <row r="465" spans="1:14" ht="72" x14ac:dyDescent="0.3">
@@ -27558,19 +27660,19 @@
         <v>509</v>
       </c>
       <c r="G465" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H465" s="2">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="I465" s="2">
-        <v>49.99</v>
+        <v>23</v>
       </c>
       <c r="J465" s="2" t="s">
         <v>18</v>
       </c>
       <c r="K465" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="L465" s="2" t="s">
         <v>25</v>
@@ -27579,7 +27681,7 @@
         <v>1</v>
       </c>
       <c r="N465" s="2" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
     </row>
     <row r="466" spans="1:14" ht="72" x14ac:dyDescent="0.3">
@@ -27593,28 +27695,28 @@
         <v>2147</v>
       </c>
       <c r="D466" s="2" t="s">
-        <v>126</v>
+        <v>1411</v>
       </c>
       <c r="E466" s="2" t="s">
-        <v>177</v>
+        <v>44</v>
       </c>
       <c r="F466" s="2" t="s">
-        <v>509</v>
+        <v>422</v>
       </c>
       <c r="G466" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H466" s="2">
-        <v>50</v>
+        <v>197.38</v>
       </c>
       <c r="I466" s="2">
-        <v>23</v>
+        <v>124.06</v>
       </c>
       <c r="J466" s="2" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="K466" s="2" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="L466" s="2" t="s">
         <v>25</v>
@@ -27626,75 +27728,31 @@
         <v>20</v>
       </c>
     </row>
-    <row r="467" spans="1:14" ht="72" x14ac:dyDescent="0.3">
-      <c r="A467" s="2" t="s">
-        <v>2148</v>
-      </c>
-      <c r="B467" s="2" t="s">
-        <v>2149</v>
-      </c>
-      <c r="C467" s="2" t="s">
-        <v>2150</v>
-      </c>
-      <c r="D467" s="2" t="s">
-        <v>1411</v>
-      </c>
-      <c r="E467" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F467" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="G467" s="2">
-        <v>20</v>
-      </c>
-      <c r="H467" s="2">
-        <v>197.38</v>
-      </c>
-      <c r="I467" s="2">
-        <v>124.06</v>
-      </c>
-      <c r="J467" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="K467" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L467" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M467" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N467" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:N467" xr:uid="{0B8C3707-A9DE-471F-806A-6A27068CFE5F}"/>
+  <autoFilter ref="A1:N466" xr:uid="{0B8C3707-A9DE-471F-806A-6A27068CFE5F}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9ECB3D7D-793F-434F-AB70-164A6EBB49D9}">
-  <dimension ref="B2:O6"/>
+  <dimension ref="B2:O10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="4" spans="2:15" ht="72" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>2076</v>
+        <v>2073</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>2077</v>
+        <v>2074</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>2078</v>
+        <v>2075</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>821</v>
@@ -27774,48 +27832,224 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="2:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:15" ht="72" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
+        <v>2155</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>2156</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>2157</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>2158</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>2159</v>
       </c>
-      <c r="D6" s="5">
-        <v>9303214</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>2160</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>2161</v>
-      </c>
       <c r="G6" s="4" t="s">
-        <v>2162</v>
-      </c>
-      <c r="H6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="I6" s="5">
+      <c r="H6" s="5">
         <v>30</v>
       </c>
+      <c r="I6" s="6">
+        <v>329.3</v>
+      </c>
       <c r="J6" s="6">
-        <v>329.3</v>
-      </c>
-      <c r="K6" s="6">
         <v>235.37</v>
       </c>
+      <c r="K6" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="L6" s="4" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="M6" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="N6" s="4" t="s">
+      <c r="N6" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="2:15" ht="72" x14ac:dyDescent="0.3">
+      <c r="B7" s="7" t="s">
+        <v>2160</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>2161</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>2162</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>895</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="8">
+        <v>30</v>
+      </c>
+      <c r="I7" s="8">
+        <v>424</v>
+      </c>
+      <c r="J7" s="8">
+        <v>302.2</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L7" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="O6" s="4" t="b">
-        <v>1</v>
+      <c r="M7" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="N7" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="O7" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="2:15" ht="72" x14ac:dyDescent="0.3">
+      <c r="B8" s="10" t="s">
+        <v>2163</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>2164</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>2165</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>899</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>900</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="H8" s="11">
+        <v>60</v>
+      </c>
+      <c r="I8" s="11">
+        <v>425</v>
+      </c>
+      <c r="J8" s="11">
+        <v>216.78</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="N8" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="O8" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="2:15" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="B9" s="7" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>2167</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>2168</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>1033</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>1034</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="H9" s="8">
+        <v>30</v>
+      </c>
+      <c r="I9" s="8">
+        <v>483</v>
+      </c>
+      <c r="J9" s="8">
+        <v>227.04</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="N9" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="O9" s="9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="2:15" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="B10" s="10" t="s">
+        <v>2169</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>2170</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>2171</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>1033</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>2172</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="H10" s="11">
+        <v>30</v>
+      </c>
+      <c r="I10" s="11">
+        <v>483.1</v>
+      </c>
+      <c r="J10" s="11">
+        <v>202.71</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="N10" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="O10" s="12" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -27833,10 +28067,10 @@
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
-        <v>2152</v>
+        <v>2149</v>
       </c>
       <c r="P2" t="s">
-        <v>2153</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="3" spans="2:16" ht="72" x14ac:dyDescent="0.3">
@@ -27883,7 +28117,7 @@
         <v>20</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>2154</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="4" spans="2:16" ht="72" x14ac:dyDescent="0.3">
@@ -27930,7 +28164,7 @@
         <v>51</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>2155</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="5" spans="2:16" ht="115.2" x14ac:dyDescent="0.3">
@@ -27977,7 +28211,7 @@
         <v>51</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>2156</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="6" spans="2:16" ht="72" x14ac:dyDescent="0.3">
@@ -28024,12 +28258,12 @@
         <v>51</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>2156</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>2157</v>
+        <v>2154</v>
       </c>
     </row>
   </sheetData>
